--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -14,12 +14,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>WSL2</t>
   </si>
   <si>
     <t>VS Code</t>
+  </si>
+  <si>
+    <t>Terraform</t>
+  </si>
+  <si>
+    <t>ArgoCD</t>
+  </si>
+  <si>
+    <t>Kubernetes(Minikube)</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
+  </si>
+  <si>
+    <t>GitHub Actions</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Dynatrace</t>
+  </si>
+  <si>
+    <t>Docker</t>
   </si>
 </sst>
 </file>
@@ -35,7 +59,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -57,6 +81,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -88,12 +118,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,27 +449,51 @@
       <c r="B2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -456,43 +456,43 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B10" s="4"/>
     </row>
@@ -507,9 +507,6 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -22,9 +22,6 @@
     <t>VS Code</t>
   </si>
   <si>
-    <t>Terraform</t>
-  </si>
-  <si>
     <t>ArgoCD</t>
   </si>
   <si>
@@ -44,6 +41,9 @@
   </si>
   <si>
     <t>Docker</t>
+  </si>
+  <si>
+    <t>Terraform(IaC)</t>
   </si>
 </sst>
 </file>
@@ -450,49 +450,49 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4"/>
     </row>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -118,13 +118,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,16 +498,19 @@
       <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
+      <c r="B12" s="6"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="4"/>
+      <c r="B13" s="6"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4"/>
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9615"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9285" windowHeight="3690"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -483,7 +483,7 @@
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">

--- a/checkboxes.xlsx
+++ b/checkboxes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9285" windowHeight="3690"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9615"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>WSL2</t>
   </si>
@@ -31,19 +31,16 @@
     <t>Jenkins</t>
   </si>
   <si>
-    <t>GitHub Actions</t>
-  </si>
-  <si>
     <t>Python</t>
   </si>
   <si>
-    <t>Dynatrace</t>
-  </si>
-  <si>
     <t>Docker</t>
   </si>
   <si>
     <t>Terraform(IaC)</t>
+  </si>
+  <si>
+    <t>Grafana</t>
   </si>
 </sst>
 </file>
@@ -451,19 +448,19 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" s="5"/>
     </row>
@@ -471,31 +468,25 @@
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6"/>
